--- a/samples/ss_sktni_ingest.xlsx
+++ b/samples/ss_sktni_ingest.xlsx
@@ -632,31 +632,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -703,27 +693,21 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -770,27 +754,21 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -819,31 +797,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -872,23 +840,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>Trf 1,2</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -904,7 +865,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -933,31 +893,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -986,19 +936,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1014,7 +956,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1043,31 +984,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1096,17 +1027,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>batas ke Subsistem Bekasi 1,3 - Cibinong 3</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1122,13 +1047,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1157,17 +1080,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cibatu 3,4</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1183,13 +1100,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1218,17 +1133,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cibatu 3,4</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1244,13 +1153,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1279,17 +1186,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cibatu 3,4</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1305,13 +1206,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1443,7 +1342,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -1457,8 +1355,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1475,13 +1371,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>SUTT New Sukatani - Bekasi (arah UP2B Jakban)</t>
@@ -1502,7 +1396,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -1516,8 +1409,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1534,13 +1425,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>SUTT Sukatani - Mitsuda</t>
@@ -1561,7 +1450,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -1575,8 +1463,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1593,7 +1479,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1624,7 +1509,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -1638,8 +1522,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1656,13 +1538,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>SUTT Kesambi Baru - Dawuan</t>
@@ -1683,7 +1563,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -1697,8 +1576,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1715,13 +1592,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>SUTT Mitsuda - Tegal Tanjung Baru (arah SS Cibatu 3,4)</t>
@@ -1742,7 +1617,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1756,8 +1630,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1774,13 +1646,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>SUTT Mitsuda - Indramayu Baru (arah SS Cibatu 3,4)</t>
@@ -1801,7 +1671,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1815,8 +1684,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1833,13 +1700,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>SUTT Mitsuda - Maligi/Katomukti (arah SS Cibatu 3,4)</t>
@@ -1860,7 +1725,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -1874,8 +1738,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1892,7 +1754,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1997,8 +1858,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2037,8 +1896,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2077,8 +1934,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2117,8 +1972,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2202,7 +2055,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Rekonduktoring Outlet GITET Sukatani (Kosambi Baru- Sukatani). Sesuai RUPTL 2025- 2034 COD 2025</t>
+          <t>Jangka Pendek: Rekonduktoring Outlet GITET Sukatani (Kosambi Baru- Sukatani). Sesuai RUPTL 2025 - 2034 COD 2025</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2090,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Rekonduktoring Outlet GITET Sukatani (Kosambi Baru- Sukatani). Sesuai RUPTL 2025- 2034 COD 2025</t>
+          <t>Jangka Pendek: Rekonduktoring Outlet GITET Sukatani (Kosambi Baru- Sukatani). Sesuai RUPTL 2025 - 2034 COD 2025</t>
         </is>
       </c>
     </row>
